--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.98219832593119</v>
+        <v>4.059607227963818</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1856798226292</v>
+        <v>4.092672971177246</v>
       </c>
       <c r="E2" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F2" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.43156190791207</v>
+        <v>5.595128810035711</v>
       </c>
       <c r="D3" t="n">
-        <v>34.57911643643916</v>
+        <v>5.619106420921365</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F3" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.01936355339107</v>
+        <v>4.390646577426049</v>
       </c>
       <c r="D4" t="n">
-        <v>27.23505593514</v>
+        <v>4.42569658946025</v>
       </c>
       <c r="E4" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F4" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.57359403734997</v>
+        <v>4.643209031069371</v>
       </c>
       <c r="D5" t="n">
-        <v>28.68011654988819</v>
+        <v>4.660518939356831</v>
       </c>
       <c r="E5" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F5" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.91649269650437</v>
+        <v>7.78643006318196</v>
       </c>
       <c r="D6" t="n">
-        <v>47.89284799358172</v>
+        <v>7.78258779895703</v>
       </c>
       <c r="E6" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F6" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.90310238280542</v>
+        <v>1.93425413720588</v>
       </c>
       <c r="D7" t="n">
-        <v>11.86810658285808</v>
+        <v>1.928567319714438</v>
       </c>
       <c r="E7" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>105.2841782442172</v>
+        <v>17.10867896468529</v>
       </c>
       <c r="D8" t="n">
-        <v>105.2715140070025</v>
+        <v>17.10662102613791</v>
       </c>
       <c r="E8" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F8" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.197842848886296</v>
+        <v>1.332149462944023</v>
       </c>
       <c r="D9" t="n">
-        <v>8.206719892012728</v>
+        <v>1.333591982452068</v>
       </c>
       <c r="E9" t="n">
-        <v>28.6259584440972</v>
+        <v>4.651718247165795</v>
       </c>
       <c r="F9" t="n">
-        <v>28.6008412206094</v>
+        <v>4.647636698349027</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
